--- a/sql/存储过程.xlsx
+++ b/sql/存储过程.xlsx
@@ -29,7 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>存储过程名称</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
   <si>
     <t xml:space="preserve">LuoDeng_getAlltableInfo  </t>
   </si>
@@ -1106,275 +1115,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="66.375" customWidth="1"/>
     <col min="3" max="3" width="55.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:3">
-      <c r="A1">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="19.5" spans="1:3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="19.5" spans="1:3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="19.5" spans="1:3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="19.5" spans="1:3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="19.5" spans="1:3">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="19.5" spans="1:3">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="19.5" spans="1:3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="19.5" spans="1:3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="19.5" spans="1:3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="19.5" spans="1:3">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="19.5" spans="1:3">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="19.5" spans="1:3">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="19.5" spans="1:3">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="19.5" spans="1:3">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="19.5" spans="1:3">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" ht="19.5" spans="1:3">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="19.5" spans="1:3">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" ht="19.5" spans="1:3">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" ht="19.5" spans="1:3">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="19.5" spans="1:3">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" ht="19.5" spans="1:3">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" ht="19.5" spans="1:3">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" ht="19.5" spans="1:3">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="25" ht="19.5" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/sql/存储过程.xlsx
+++ b/sql/存储过程.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>序号</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>获取消息代码信息</t>
+  </si>
+  <si>
+    <t>usp_getXsjlkData</t>
+  </si>
+  <si>
+    <t>获取学生简历</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="66.375" customWidth="1"/>
@@ -1395,6 +1401,14 @@
       </c>
       <c r="C25" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
